--- a/MODELLO_SCHEDA_PRODUZIONE.xlsx
+++ b/MODELLO_SCHEDA_PRODUZIONE.xlsx
@@ -1296,7 +1296,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.0546875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
@@ -2273,6 +2273,6 @@
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/MODELLO_SCHEDA_PRODUZIONE.xlsx
+++ b/MODELLO_SCHEDA_PRODUZIONE.xlsx
@@ -2273,6 +2273,6 @@
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/MODELLO_SCHEDA_PRODUZIONE.xlsx
+++ b/MODELLO_SCHEDA_PRODUZIONE.xlsx
@@ -1296,9 +1296,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.0546875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3.85" customWidth="1" style="45" min="1" max="1"/>
@@ -1320,17 +1320,9 @@
           <t>SCHEDA DI LAVORAZIONE E RINTRACCIABILITA'</t>
         </is>
       </c>
-      <c r="J1" s="48" t="n"/>
-      <c r="K1" s="48" t="n"/>
-    </row>
-    <row r="2" ht="12.75" customHeight="1" s="46">
-      <c r="J2" s="48" t="n"/>
-      <c r="K2" s="48" t="n"/>
-    </row>
-    <row r="3" ht="12.75" customHeight="1" s="46">
-      <c r="J3" s="48" t="n"/>
-      <c r="K3" s="48" t="n"/>
-    </row>
+    </row>
+    <row r="2" ht="12.75" customHeight="1" s="46"/>
+    <row r="3" ht="12.75" customHeight="1" s="46"/>
     <row r="4" ht="18" customHeight="1" s="46">
       <c r="C4" s="49" t="inlineStr">
         <is>
@@ -1405,31 +1397,6 @@
           <t>MATERIA PRIMA UTILIZZATA</t>
         </is>
       </c>
-      <c r="J11" s="69" t="inlineStr">
-        <is>
-          <t>Kg x Fto</t>
-        </is>
-      </c>
-      <c r="K11" s="69" t="inlineStr">
-        <is>
-          <t>Kg x Fto</t>
-        </is>
-      </c>
-      <c r="L11" s="69" t="inlineStr">
-        <is>
-          <t>Kg x Fto</t>
-        </is>
-      </c>
-      <c r="M11" s="69" t="inlineStr">
-        <is>
-          <t>Kg x Fto</t>
-        </is>
-      </c>
-      <c r="N11" s="70" t="inlineStr">
-        <is>
-          <t>Kg x Fto</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="12.75" customHeight="1" s="46">
       <c r="A12" s="70" t="inlineStr">
@@ -1464,21 +1431,6 @@
         <is>
           <t>UM</t>
         </is>
-      </c>
-      <c r="J12" s="69" t="n">
-        <v>212</v>
-      </c>
-      <c r="K12" s="69" t="n">
-        <v>314</v>
-      </c>
-      <c r="L12" s="69" t="n">
-        <v>106</v>
-      </c>
-      <c r="M12" s="69" t="n">
-        <v>1062</v>
-      </c>
-      <c r="N12" s="70" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1" s="46">
@@ -1493,26 +1445,6 @@
       <c r="G13" s="75" t="n"/>
       <c r="H13" s="74" t="n"/>
       <c r="I13" s="74" t="n"/>
-      <c r="J13" s="77">
-        <f>H13*L28/100</f>
-        <v/>
-      </c>
-      <c r="K13" s="78">
-        <f>H13*L30/100</f>
-        <v/>
-      </c>
-      <c r="L13" s="77">
-        <f>H13*L29/100</f>
-        <v/>
-      </c>
-      <c r="M13" s="78">
-        <f>H13*L31/100</f>
-        <v/>
-      </c>
-      <c r="N13" s="77">
-        <f>H13*L32/100</f>
-        <v/>
-      </c>
     </row>
     <row r="14" ht="12.75" customHeight="1" s="46">
       <c r="A14" s="74" t="n">
@@ -1526,26 +1458,6 @@
       <c r="G14" s="75" t="n"/>
       <c r="H14" s="74" t="n"/>
       <c r="I14" s="74" t="n"/>
-      <c r="J14" s="77">
-        <f>H14*L28/100</f>
-        <v/>
-      </c>
-      <c r="K14" s="78">
-        <f>H14*L30/100</f>
-        <v/>
-      </c>
-      <c r="L14" s="77">
-        <f>H14*L29/100</f>
-        <v/>
-      </c>
-      <c r="M14" s="78">
-        <f>H14*L31/100</f>
-        <v/>
-      </c>
-      <c r="N14" s="77">
-        <f>H14*L32/100</f>
-        <v/>
-      </c>
     </row>
     <row r="15" ht="12.75" customHeight="1" s="46">
       <c r="A15" s="74" t="n">
@@ -1559,11 +1471,6 @@
       <c r="G15" s="75" t="n"/>
       <c r="H15" s="74" t="n"/>
       <c r="I15" s="74" t="n"/>
-      <c r="J15" s="81" t="n"/>
-      <c r="L15" s="82" t="n"/>
-      <c r="M15" s="82" t="n"/>
-      <c r="N15" s="82" t="n"/>
-      <c r="O15" s="82" t="n"/>
     </row>
     <row r="16" ht="12.75" customHeight="1" s="46">
       <c r="A16" s="74" t="n">
@@ -1577,11 +1484,6 @@
       <c r="G16" s="75" t="n"/>
       <c r="H16" s="74" t="n"/>
       <c r="I16" s="74" t="n"/>
-      <c r="J16" s="81" t="n"/>
-      <c r="L16" s="82" t="n"/>
-      <c r="M16" s="82" t="n"/>
-      <c r="N16" s="82" t="n"/>
-      <c r="O16" s="82" t="n"/>
     </row>
     <row r="17" ht="12.75" customHeight="1" s="46">
       <c r="A17" s="74" t="n">
@@ -1595,11 +1497,6 @@
       <c r="G17" s="75" t="n"/>
       <c r="H17" s="74" t="n"/>
       <c r="I17" s="74" t="n"/>
-      <c r="J17" s="81" t="n"/>
-      <c r="L17" s="82" t="n"/>
-      <c r="M17" s="82" t="n"/>
-      <c r="N17" s="82" t="n"/>
-      <c r="O17" s="82" t="n"/>
     </row>
     <row r="18" ht="12.75" customHeight="1" s="46">
       <c r="A18" s="74" t="n">
@@ -1613,11 +1510,6 @@
       <c r="G18" s="75" t="n"/>
       <c r="H18" s="74" t="n"/>
       <c r="I18" s="74" t="n"/>
-      <c r="J18" s="81" t="n"/>
-      <c r="L18" s="82" t="n"/>
-      <c r="M18" s="82" t="n"/>
-      <c r="N18" s="82" t="n"/>
-      <c r="O18" s="82" t="n"/>
     </row>
     <row r="19" ht="12.75" customHeight="1" s="46">
       <c r="A19" s="74" t="n">
@@ -1631,11 +1523,6 @@
       <c r="G19" s="75" t="n"/>
       <c r="H19" s="74" t="n"/>
       <c r="I19" s="74" t="n"/>
-      <c r="J19" s="81" t="n"/>
-      <c r="L19" s="82" t="n"/>
-      <c r="M19" s="82" t="n"/>
-      <c r="N19" s="82" t="n"/>
-      <c r="O19" s="82" t="n"/>
     </row>
     <row r="20" ht="12.75" customHeight="1" s="46">
       <c r="A20" s="74" t="n">
@@ -1649,11 +1536,6 @@
       <c r="G20" s="75" t="n"/>
       <c r="H20" s="74" t="n"/>
       <c r="I20" s="74" t="n"/>
-      <c r="J20" s="81" t="n"/>
-      <c r="L20" s="82" t="n"/>
-      <c r="M20" s="82" t="n"/>
-      <c r="N20" s="82" t="n"/>
-      <c r="O20" s="82" t="n"/>
     </row>
     <row r="21" ht="12.75" customHeight="1" s="46">
       <c r="A21" s="74" t="n">
@@ -1667,12 +1549,6 @@
       <c r="G21" s="75" t="n"/>
       <c r="H21" s="74" t="n"/>
       <c r="I21" s="74" t="n"/>
-      <c r="J21" s="81" t="n"/>
-      <c r="K21" s="82" t="n"/>
-      <c r="L21" s="82" t="n"/>
-      <c r="M21" s="82" t="n"/>
-      <c r="N21" s="82" t="n"/>
-      <c r="O21" s="82" t="n"/>
     </row>
     <row r="22" ht="12.75" customHeight="1" s="46">
       <c r="A22" s="74" t="n">
@@ -1686,12 +1562,6 @@
       <c r="G22" s="75" t="n"/>
       <c r="H22" s="74" t="n"/>
       <c r="I22" s="74" t="n"/>
-      <c r="J22" s="81" t="n"/>
-      <c r="K22" s="82" t="n"/>
-      <c r="L22" s="82" t="n"/>
-      <c r="M22" s="82" t="n"/>
-      <c r="N22" s="82" t="n"/>
-      <c r="O22" s="82" t="n"/>
     </row>
     <row r="23" ht="12.75" customHeight="1" s="46">
       <c r="A23" s="74" t="n">
@@ -1705,12 +1575,6 @@
       <c r="G23" s="75" t="n"/>
       <c r="H23" s="74" t="n"/>
       <c r="I23" s="74" t="n"/>
-      <c r="J23" s="81" t="n"/>
-      <c r="K23" s="82" t="n"/>
-      <c r="L23" s="82" t="n"/>
-      <c r="M23" s="82" t="n"/>
-      <c r="N23" s="82" t="n"/>
-      <c r="O23" s="82" t="n"/>
     </row>
     <row r="24" ht="12.75" customHeight="1" s="46">
       <c r="A24" s="74" t="n">
@@ -1724,12 +1588,6 @@
       <c r="G24" s="75" t="n"/>
       <c r="H24" s="74" t="n"/>
       <c r="I24" s="74" t="n"/>
-      <c r="J24" s="81" t="n"/>
-      <c r="K24" s="82" t="n"/>
-      <c r="L24" s="82" t="n"/>
-      <c r="M24" s="82" t="n"/>
-      <c r="N24" s="82" t="n"/>
-      <c r="O24" s="82" t="n"/>
     </row>
     <row r="25" ht="12.75" customHeight="1" s="46">
       <c r="A25" s="74" t="n">
@@ -1743,12 +1601,6 @@
       <c r="G25" s="75" t="n"/>
       <c r="H25" s="74" t="n"/>
       <c r="I25" s="74" t="n"/>
-      <c r="J25" s="81" t="n"/>
-      <c r="K25" s="82" t="n"/>
-      <c r="L25" s="82" t="n"/>
-      <c r="M25" s="82" t="n"/>
-      <c r="N25" s="82" t="n"/>
-      <c r="O25" s="82" t="n"/>
     </row>
     <row r="26" ht="12.75" customHeight="1" s="46">
       <c r="A26" s="74" t="n">
@@ -1762,12 +1614,6 @@
       <c r="G26" s="75" t="n"/>
       <c r="H26" s="74" t="n"/>
       <c r="I26" s="74" t="n"/>
-      <c r="J26" s="81" t="n"/>
-      <c r="K26" s="82" t="n"/>
-      <c r="L26" s="82" t="n"/>
-      <c r="M26" s="82" t="n"/>
-      <c r="N26" s="82" t="n"/>
-      <c r="O26" s="82" t="n"/>
     </row>
     <row r="27" ht="12.75" customHeight="1" s="46">
       <c r="A27" s="74" t="n">
@@ -1781,12 +1627,6 @@
       <c r="G27" s="75" t="n"/>
       <c r="H27" s="84" t="n"/>
       <c r="I27" s="84" t="n"/>
-      <c r="K27" s="87" t="n"/>
-      <c r="L27" s="71" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
     </row>
     <row r="28" ht="12.75" customHeight="1" s="46">
       <c r="A28" s="74" t="n">
@@ -1800,15 +1640,6 @@
       <c r="G28" s="75" t="n"/>
       <c r="H28" s="84" t="n"/>
       <c r="I28" s="80" t="n"/>
-      <c r="K28" s="87" t="inlineStr">
-        <is>
-          <t>Fto 212</t>
-        </is>
-      </c>
-      <c r="L28" s="88">
-        <f>IF(SUM($C$40:$C$44)=0,0,C41*100/SUM($C$40:$C$44))</f>
-        <v/>
-      </c>
     </row>
     <row r="29" ht="12.75" customHeight="1" s="46">
       <c r="A29" s="74" t="n">
@@ -1822,15 +1653,6 @@
       <c r="G29" s="75" t="n"/>
       <c r="H29" s="84" t="n"/>
       <c r="I29" s="80" t="n"/>
-      <c r="K29" s="87" t="inlineStr">
-        <is>
-          <t>Fto 106</t>
-        </is>
-      </c>
-      <c r="L29" s="88">
-        <f>IF(SUM($C$40:$C$44)=0,0,C43*100/SUM($C$40:$C$44))</f>
-        <v/>
-      </c>
     </row>
     <row r="30" ht="12.75" customHeight="1" s="46">
       <c r="A30" s="74" t="n">
@@ -1844,15 +1666,6 @@
       <c r="G30" s="75" t="n"/>
       <c r="H30" s="84" t="n"/>
       <c r="I30" s="80" t="n"/>
-      <c r="K30" s="87" t="inlineStr">
-        <is>
-          <t>Fto 314</t>
-        </is>
-      </c>
-      <c r="L30" s="88">
-        <f>IF(SUM($C$40:$C$44)=0,0,C42*100/SUM($C$40:$C$44))</f>
-        <v/>
-      </c>
     </row>
     <row r="31" ht="12.75" customHeight="1" s="46">
       <c r="A31" s="74" t="n">
@@ -1866,15 +1679,6 @@
       <c r="G31" s="75" t="n"/>
       <c r="H31" s="84" t="n"/>
       <c r="I31" s="80" t="n"/>
-      <c r="K31" s="87" t="inlineStr">
-        <is>
-          <t>Fto 1062</t>
-        </is>
-      </c>
-      <c r="L31" s="88">
-        <f>IF(SUM($C$40:$C$44)=0,0,C44*100/SUM($C$40:$C$44))</f>
-        <v/>
-      </c>
     </row>
     <row r="32" ht="12.75" customHeight="1" s="46">
       <c r="A32" s="74" t="n">
@@ -1888,15 +1692,6 @@
       <c r="G32" s="75" t="n"/>
       <c r="H32" s="84" t="n"/>
       <c r="I32" s="80" t="n"/>
-      <c r="K32" s="87" t="inlineStr">
-        <is>
-          <t>Fto 40</t>
-        </is>
-      </c>
-      <c r="L32" s="88">
-        <f>IF(SUM($C$40:$C$44)=0,0,C40*100/SUM($C$40:$C$44))</f>
-        <v/>
-      </c>
     </row>
     <row r="33" ht="12.75" customHeight="1" s="46">
       <c r="A33" s="74" t="n">
@@ -2271,8 +2066,8 @@
     <mergeCell ref="G48:I48"/>
     <mergeCell ref="E47:F47"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="88" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/MODELLO_SCHEDA_PRODUZIONE.xlsx
+++ b/MODELLO_SCHEDA_PRODUZIONE.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHEDA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'SCHEDA'!$A$1:$I$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'SCHEDA'!$A$1:$I$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -25,7 +25,7 @@
     <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss"/>
     <numFmt numFmtId="168" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="33">
     <font>
       <name val="Arial"/>
       <charset val="1"/>
@@ -238,6 +238,19 @@
       <family val="2"/>
       <b val="1"/>
       <sz val="22"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="25">
@@ -726,7 +739,7 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1065,6 +1078,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="47">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1298,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.0546875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3.85" customWidth="1" style="45" min="1" max="1"/>
@@ -1314,206 +1342,188 @@
     <col width="8.56" customWidth="1" style="45" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1" s="46">
-      <c r="A1" s="47" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="46">
+      <c r="A1" s="108" t="inlineStr">
+        <is>
+          <t>AZIENDA SCALZO DI GAROFALO CARMELINA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1" s="46">
+      <c r="A2" s="109" t="inlineStr">
+        <is>
+          <t>C.da Pallone – 87050 Marzi  ·  P.IVA 02093320782</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="13" customHeight="1" s="46">
+      <c r="A3" s="110" t="inlineStr">
+        <is>
+          <t>Aut. sanitaria: U.O.C. Igiene Alimenti e Nutrizione – Prot. n. 0232708 del 11/11/2013 – Reg. 078CS0564G</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="12" customHeight="1" s="46">
+      <c r="A4" s="110" t="inlineStr">
+        <is>
+          <t>ASP Provinciale – Distretto di Rogliano</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="12.75" customHeight="1" s="46">
+      <c r="A5" s="111" t="inlineStr">
         <is>
           <t>SCHEDA DI LAVORAZIONE E RINTRACCIABILITA'</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="12.75" customHeight="1" s="46"/>
-    <row r="3" ht="12.75" customHeight="1" s="46"/>
-    <row r="4" ht="18" customHeight="1" s="46">
-      <c r="C4" s="49" t="inlineStr">
+    <row r="6" ht="12.75" customHeight="1" s="46"/>
+    <row r="7" ht="12.75" customHeight="1" s="46"/>
+    <row r="8" ht="16.5" customHeight="1" s="46">
+      <c r="A8" s="112" t="inlineStr">
         <is>
           <t>Denominazione Prodotto</t>
         </is>
       </c>
-      <c r="D4" s="50" t="n"/>
-      <c r="E4" s="50" t="n"/>
-      <c r="F4" s="50" t="n"/>
-      <c r="G4" s="50" t="n"/>
-      <c r="H4" s="50" t="n"/>
-      <c r="I4" s="51" t="n"/>
-    </row>
-    <row r="5" ht="12.75" customHeight="1" s="46">
-      <c r="C5" s="52" t="n"/>
-      <c r="D5" s="53" t="n"/>
-      <c r="E5" s="53" t="n"/>
-      <c r="F5" s="53" t="n"/>
-      <c r="G5" s="53" t="n"/>
-      <c r="H5" s="53" t="n"/>
-      <c r="I5" s="54" t="n"/>
-    </row>
-    <row r="6" ht="12.75" customHeight="1" s="46">
-      <c r="C6" s="55" t="n"/>
-      <c r="D6" s="56" t="n"/>
-      <c r="E6" s="56" t="n"/>
-      <c r="F6" s="56" t="n"/>
-      <c r="G6" s="56" t="n"/>
-      <c r="H6" s="56" t="n"/>
-      <c r="I6" s="57" t="n"/>
-    </row>
-    <row r="7" ht="12.75" customHeight="1" s="46"/>
-    <row r="8" ht="12.75" customHeight="1" s="46">
-      <c r="A8" s="58" t="inlineStr">
+      <c r="B8" s="50" t="n"/>
+      <c r="C8" s="50" t="n"/>
+      <c r="D8" s="50" t="n"/>
+      <c r="E8" s="50" t="n"/>
+      <c r="F8" s="50" t="n"/>
+      <c r="G8" s="50" t="n"/>
+      <c r="H8" s="50" t="n"/>
+      <c r="I8" s="51" t="n"/>
+    </row>
+    <row r="9" ht="12.75" customHeight="1" s="46">
+      <c r="A9" s="49" t="n"/>
+      <c r="B9" s="98" t="n"/>
+      <c r="C9" s="98" t="n"/>
+      <c r="D9" s="98" t="n"/>
+      <c r="E9" s="98" t="n"/>
+      <c r="F9" s="98" t="n"/>
+      <c r="G9" s="98" t="n"/>
+      <c r="H9" s="98" t="n"/>
+      <c r="I9" s="59" t="n"/>
+    </row>
+    <row r="10" ht="12.75" customHeight="1" s="46">
+      <c r="A10" s="64" t="n"/>
+      <c r="B10" s="95" t="n"/>
+      <c r="C10" s="95" t="n"/>
+      <c r="D10" s="95" t="n"/>
+      <c r="E10" s="95" t="n"/>
+      <c r="F10" s="95" t="n"/>
+      <c r="G10" s="95" t="n"/>
+      <c r="H10" s="95" t="n"/>
+      <c r="I10" s="65" t="n"/>
+    </row>
+    <row r="11" ht="12.75" customHeight="1" s="46"/>
+    <row r="12" ht="12.75" customHeight="1" s="46">
+      <c r="A12" s="58" t="inlineStr">
         <is>
           <t>N. PROGRESSIVO
 PRODUZIONE</t>
         </is>
       </c>
-      <c r="B8" s="59" t="n"/>
-      <c r="C8" s="60" t="n"/>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="B12" s="59" t="n"/>
+      <c r="C12" s="60" t="n"/>
+      <c r="D12" s="61" t="inlineStr">
         <is>
           <t>Ore Lavorate</t>
         </is>
       </c>
-      <c r="E8" s="52" t="n"/>
-      <c r="F8" s="62" t="inlineStr">
+      <c r="E12" s="52" t="n"/>
+      <c r="F12" s="62" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="G8" s="63" t="n"/>
-      <c r="H8" s="53" t="n"/>
-      <c r="I8" s="54" t="n"/>
-    </row>
-    <row r="9" ht="12.75" customHeight="1" s="46">
-      <c r="A9" s="64" t="n"/>
-      <c r="B9" s="65" t="n"/>
-      <c r="C9" s="66" t="n"/>
-      <c r="D9" s="67" t="n"/>
-      <c r="E9" s="66" t="n"/>
-      <c r="F9" s="67" t="n"/>
-      <c r="G9" s="55" t="n"/>
-      <c r="H9" s="56" t="n"/>
-      <c r="I9" s="57" t="n"/>
-    </row>
-    <row r="10" ht="12.75" customHeight="1" s="46"/>
-    <row r="11" ht="12.75" customHeight="1" s="46">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="G12" s="63" t="n"/>
+      <c r="H12" s="53" t="n"/>
+      <c r="I12" s="54" t="n"/>
+    </row>
+    <row r="13" ht="12.75" customHeight="1" s="46">
+      <c r="A13" s="64" t="n"/>
+      <c r="B13" s="65" t="n"/>
+      <c r="C13" s="66" t="n"/>
+      <c r="D13" s="67" t="n"/>
+      <c r="E13" s="66" t="n"/>
+      <c r="F13" s="67" t="n"/>
+      <c r="G13" s="55" t="n"/>
+      <c r="H13" s="56" t="n"/>
+      <c r="I13" s="57" t="n"/>
+    </row>
+    <row r="14" ht="12.75" customHeight="1" s="46"/>
+    <row r="15" ht="12.75" customHeight="1" s="46">
+      <c r="A15" s="68" t="inlineStr">
         <is>
           <t>MATERIA PRIMA UTILIZZATA</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="12.75" customHeight="1" s="46">
-      <c r="A12" s="70" t="inlineStr">
+    <row r="16" ht="12.75" customHeight="1" s="46">
+      <c r="A16" s="70" t="inlineStr">
         <is>
           <t>N.</t>
         </is>
       </c>
-      <c r="B12" s="71" t="inlineStr">
+      <c r="B16" s="71" t="inlineStr">
         <is>
           <t>PRODOTTO</t>
         </is>
       </c>
-      <c r="C12" s="51" t="n"/>
-      <c r="D12" s="71" t="inlineStr">
+      <c r="C16" s="51" t="n"/>
+      <c r="D16" s="71" t="inlineStr">
         <is>
           <t>FORNITORE</t>
         </is>
       </c>
-      <c r="E12" s="51" t="n"/>
-      <c r="F12" s="72" t="inlineStr">
+      <c r="E16" s="51" t="n"/>
+      <c r="F16" s="72" t="inlineStr">
         <is>
           <t>LOTTO D'INGRESSO</t>
         </is>
       </c>
-      <c r="G12" s="51" t="n"/>
-      <c r="H12" s="71" t="inlineStr">
+      <c r="G16" s="51" t="n"/>
+      <c r="H16" s="71" t="inlineStr">
         <is>
           <t>Qnt</t>
         </is>
       </c>
-      <c r="I12" s="71" t="inlineStr">
+      <c r="I16" s="71" t="inlineStr">
         <is>
           <t>UM</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="12.75" customHeight="1" s="46">
-      <c r="A13" s="73" t="n">
+    <row r="17" ht="12.75" customHeight="1" s="46">
+      <c r="A17" s="73" t="n">
         <v>1</v>
-      </c>
-      <c r="B13" s="74" t="n"/>
-      <c r="C13" s="75" t="n"/>
-      <c r="D13" s="74" t="n"/>
-      <c r="E13" s="75" t="n"/>
-      <c r="F13" s="76" t="n"/>
-      <c r="G13" s="75" t="n"/>
-      <c r="H13" s="74" t="n"/>
-      <c r="I13" s="74" t="n"/>
-    </row>
-    <row r="14" ht="12.75" customHeight="1" s="46">
-      <c r="A14" s="74" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="74" t="n"/>
-      <c r="C14" s="75" t="n"/>
-      <c r="D14" s="74" t="n"/>
-      <c r="E14" s="75" t="n"/>
-      <c r="F14" s="79" t="n"/>
-      <c r="G14" s="75" t="n"/>
-      <c r="H14" s="74" t="n"/>
-      <c r="I14" s="74" t="n"/>
-    </row>
-    <row r="15" ht="12.75" customHeight="1" s="46">
-      <c r="A15" s="74" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="74" t="n"/>
-      <c r="C15" s="75" t="n"/>
-      <c r="D15" s="74" t="n"/>
-      <c r="E15" s="75" t="n"/>
-      <c r="F15" s="80" t="n"/>
-      <c r="G15" s="75" t="n"/>
-      <c r="H15" s="74" t="n"/>
-      <c r="I15" s="74" t="n"/>
-    </row>
-    <row r="16" ht="12.75" customHeight="1" s="46">
-      <c r="A16" s="74" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="74" t="n"/>
-      <c r="C16" s="75" t="n"/>
-      <c r="D16" s="74" t="n"/>
-      <c r="E16" s="75" t="n"/>
-      <c r="F16" s="83" t="n"/>
-      <c r="G16" s="75" t="n"/>
-      <c r="H16" s="74" t="n"/>
-      <c r="I16" s="74" t="n"/>
-    </row>
-    <row r="17" ht="12.75" customHeight="1" s="46">
-      <c r="A17" s="74" t="n">
-        <v>5</v>
       </c>
       <c r="B17" s="74" t="n"/>
       <c r="C17" s="75" t="n"/>
       <c r="D17" s="74" t="n"/>
       <c r="E17" s="75" t="n"/>
-      <c r="F17" s="83" t="n"/>
+      <c r="F17" s="76" t="n"/>
       <c r="G17" s="75" t="n"/>
       <c r="H17" s="74" t="n"/>
       <c r="I17" s="74" t="n"/>
     </row>
     <row r="18" ht="12.75" customHeight="1" s="46">
       <c r="A18" s="74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B18" s="74" t="n"/>
       <c r="C18" s="75" t="n"/>
       <c r="D18" s="74" t="n"/>
       <c r="E18" s="75" t="n"/>
-      <c r="F18" s="80" t="n"/>
+      <c r="F18" s="79" t="n"/>
       <c r="G18" s="75" t="n"/>
       <c r="H18" s="74" t="n"/>
       <c r="I18" s="74" t="n"/>
     </row>
     <row r="19" ht="12.75" customHeight="1" s="46">
       <c r="A19" s="74" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B19" s="74" t="n"/>
       <c r="C19" s="75" t="n"/>
@@ -1526,33 +1536,33 @@
     </row>
     <row r="20" ht="12.75" customHeight="1" s="46">
       <c r="A20" s="74" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B20" s="74" t="n"/>
       <c r="C20" s="75" t="n"/>
       <c r="D20" s="74" t="n"/>
       <c r="E20" s="75" t="n"/>
-      <c r="F20" s="80" t="n"/>
+      <c r="F20" s="83" t="n"/>
       <c r="G20" s="75" t="n"/>
       <c r="H20" s="74" t="n"/>
       <c r="I20" s="74" t="n"/>
     </row>
     <row r="21" ht="12.75" customHeight="1" s="46">
       <c r="A21" s="74" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B21" s="74" t="n"/>
       <c r="C21" s="75" t="n"/>
       <c r="D21" s="74" t="n"/>
       <c r="E21" s="75" t="n"/>
-      <c r="F21" s="80" t="n"/>
+      <c r="F21" s="83" t="n"/>
       <c r="G21" s="75" t="n"/>
       <c r="H21" s="74" t="n"/>
       <c r="I21" s="74" t="n"/>
     </row>
     <row r="22" ht="12.75" customHeight="1" s="46">
       <c r="A22" s="74" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B22" s="74" t="n"/>
       <c r="C22" s="75" t="n"/>
@@ -1565,7 +1575,7 @@
     </row>
     <row r="23" ht="12.75" customHeight="1" s="46">
       <c r="A23" s="74" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B23" s="74" t="n"/>
       <c r="C23" s="75" t="n"/>
@@ -1578,72 +1588,72 @@
     </row>
     <row r="24" ht="12.75" customHeight="1" s="46">
       <c r="A24" s="74" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B24" s="74" t="n"/>
       <c r="C24" s="75" t="n"/>
       <c r="D24" s="74" t="n"/>
       <c r="E24" s="75" t="n"/>
-      <c r="F24" s="84" t="n"/>
+      <c r="F24" s="80" t="n"/>
       <c r="G24" s="75" t="n"/>
       <c r="H24" s="74" t="n"/>
       <c r="I24" s="74" t="n"/>
     </row>
     <row r="25" ht="12.75" customHeight="1" s="46">
       <c r="A25" s="74" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B25" s="74" t="n"/>
       <c r="C25" s="75" t="n"/>
       <c r="D25" s="74" t="n"/>
       <c r="E25" s="75" t="n"/>
-      <c r="F25" s="85" t="n"/>
+      <c r="F25" s="80" t="n"/>
       <c r="G25" s="75" t="n"/>
       <c r="H25" s="74" t="n"/>
       <c r="I25" s="74" t="n"/>
     </row>
     <row r="26" ht="12.75" customHeight="1" s="46">
       <c r="A26" s="74" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B26" s="74" t="n"/>
       <c r="C26" s="75" t="n"/>
       <c r="D26" s="74" t="n"/>
       <c r="E26" s="75" t="n"/>
-      <c r="F26" s="85" t="n"/>
+      <c r="F26" s="80" t="n"/>
       <c r="G26" s="75" t="n"/>
       <c r="H26" s="74" t="n"/>
       <c r="I26" s="74" t="n"/>
     </row>
     <row r="27" ht="12.75" customHeight="1" s="46">
       <c r="A27" s="74" t="n">
-        <v>15</v>
-      </c>
-      <c r="B27" s="86" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="B27" s="74" t="n"/>
       <c r="C27" s="75" t="n"/>
-      <c r="D27" s="86" t="n"/>
+      <c r="D27" s="74" t="n"/>
       <c r="E27" s="75" t="n"/>
-      <c r="F27" s="85" t="n"/>
+      <c r="F27" s="80" t="n"/>
       <c r="G27" s="75" t="n"/>
-      <c r="H27" s="84" t="n"/>
-      <c r="I27" s="84" t="n"/>
+      <c r="H27" s="74" t="n"/>
+      <c r="I27" s="74" t="n"/>
     </row>
     <row r="28" ht="12.75" customHeight="1" s="46">
       <c r="A28" s="74" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B28" s="74" t="n"/>
       <c r="C28" s="75" t="n"/>
       <c r="D28" s="74" t="n"/>
       <c r="E28" s="75" t="n"/>
-      <c r="F28" s="85" t="n"/>
+      <c r="F28" s="84" t="n"/>
       <c r="G28" s="75" t="n"/>
-      <c r="H28" s="84" t="n"/>
-      <c r="I28" s="80" t="n"/>
+      <c r="H28" s="74" t="n"/>
+      <c r="I28" s="74" t="n"/>
     </row>
     <row r="29" ht="12.75" customHeight="1" s="46">
       <c r="A29" s="74" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B29" s="74" t="n"/>
       <c r="C29" s="75" t="n"/>
@@ -1651,12 +1661,12 @@
       <c r="E29" s="75" t="n"/>
       <c r="F29" s="85" t="n"/>
       <c r="G29" s="75" t="n"/>
-      <c r="H29" s="84" t="n"/>
-      <c r="I29" s="80" t="n"/>
+      <c r="H29" s="74" t="n"/>
+      <c r="I29" s="74" t="n"/>
     </row>
     <row r="30" ht="12.75" customHeight="1" s="46">
       <c r="A30" s="74" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B30" s="74" t="n"/>
       <c r="C30" s="75" t="n"/>
@@ -1664,25 +1674,25 @@
       <c r="E30" s="75" t="n"/>
       <c r="F30" s="85" t="n"/>
       <c r="G30" s="75" t="n"/>
-      <c r="H30" s="84" t="n"/>
-      <c r="I30" s="80" t="n"/>
+      <c r="H30" s="74" t="n"/>
+      <c r="I30" s="74" t="n"/>
     </row>
     <row r="31" ht="12.75" customHeight="1" s="46">
       <c r="A31" s="74" t="n">
-        <v>19</v>
-      </c>
-      <c r="B31" s="74" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="B31" s="86" t="n"/>
       <c r="C31" s="75" t="n"/>
-      <c r="D31" s="74" t="n"/>
+      <c r="D31" s="86" t="n"/>
       <c r="E31" s="75" t="n"/>
       <c r="F31" s="85" t="n"/>
       <c r="G31" s="75" t="n"/>
       <c r="H31" s="84" t="n"/>
-      <c r="I31" s="80" t="n"/>
+      <c r="I31" s="84" t="n"/>
     </row>
     <row r="32" ht="12.75" customHeight="1" s="46">
       <c r="A32" s="74" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B32" s="74" t="n"/>
       <c r="C32" s="75" t="n"/>
@@ -1695,7 +1705,7 @@
     </row>
     <row r="33" ht="12.75" customHeight="1" s="46">
       <c r="A33" s="74" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B33" s="74" t="n"/>
       <c r="C33" s="75" t="n"/>
@@ -1707,157 +1717,149 @@
       <c r="I33" s="80" t="n"/>
     </row>
     <row r="34" ht="12.75" customHeight="1" s="46">
-      <c r="D34" s="89" t="n"/>
-      <c r="E34" s="89" t="n"/>
-      <c r="F34" s="89" t="n"/>
-      <c r="G34" s="89" t="n"/>
-    </row>
-    <row r="35" ht="25.5" customHeight="1" s="46">
-      <c r="A35" s="90" t="inlineStr">
+      <c r="A34" s="74" t="n">
+        <v>18</v>
+      </c>
+      <c r="B34" s="74" t="n"/>
+      <c r="C34" s="75" t="n"/>
+      <c r="D34" s="74" t="n"/>
+      <c r="E34" s="75" t="n"/>
+      <c r="F34" s="85" t="n"/>
+      <c r="G34" s="75" t="n"/>
+      <c r="H34" s="84" t="n"/>
+      <c r="I34" s="80" t="n"/>
+    </row>
+    <row r="35" ht="12.75" customHeight="1" s="46">
+      <c r="A35" s="74" t="n">
+        <v>19</v>
+      </c>
+      <c r="B35" s="74" t="n"/>
+      <c r="C35" s="75" t="n"/>
+      <c r="D35" s="74" t="n"/>
+      <c r="E35" s="75" t="n"/>
+      <c r="F35" s="85" t="n"/>
+      <c r="G35" s="75" t="n"/>
+      <c r="H35" s="84" t="n"/>
+      <c r="I35" s="80" t="n"/>
+    </row>
+    <row r="36" ht="12.75" customHeight="1" s="46">
+      <c r="A36" s="74" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" s="74" t="n"/>
+      <c r="C36" s="75" t="n"/>
+      <c r="D36" s="74" t="n"/>
+      <c r="E36" s="75" t="n"/>
+      <c r="F36" s="85" t="n"/>
+      <c r="G36" s="75" t="n"/>
+      <c r="H36" s="84" t="n"/>
+      <c r="I36" s="80" t="n"/>
+    </row>
+    <row r="37" ht="12.75" customHeight="1" s="46">
+      <c r="A37" s="74" t="n">
+        <v>21</v>
+      </c>
+      <c r="B37" s="74" t="n"/>
+      <c r="C37" s="75" t="n"/>
+      <c r="D37" s="74" t="n"/>
+      <c r="E37" s="75" t="n"/>
+      <c r="F37" s="85" t="n"/>
+      <c r="G37" s="75" t="n"/>
+      <c r="H37" s="84" t="n"/>
+      <c r="I37" s="80" t="n"/>
+    </row>
+    <row r="38" ht="12.75" customHeight="1" s="46">
+      <c r="D38" s="89" t="n"/>
+      <c r="E38" s="89" t="n"/>
+      <c r="F38" s="89" t="n"/>
+      <c r="G38" s="89" t="n"/>
+    </row>
+    <row r="39" ht="25.5" customHeight="1" s="46">
+      <c r="A39" s="90" t="inlineStr">
         <is>
           <t>PH</t>
         </is>
       </c>
-      <c r="B35" s="51" t="n"/>
-      <c r="C35" s="91" t="n"/>
-      <c r="D35" s="87" t="n"/>
-      <c r="E35" s="92" t="inlineStr">
+      <c r="B39" s="51" t="n"/>
+      <c r="C39" s="91" t="n"/>
+      <c r="D39" s="87" t="n"/>
+      <c r="E39" s="92" t="inlineStr">
         <is>
           <t>TEMPERATURA DI
 PASTORIZZAZIONE</t>
         </is>
       </c>
-      <c r="F35" s="51" t="n"/>
-      <c r="G35" s="91" t="inlineStr">
+      <c r="F39" s="51" t="n"/>
+      <c r="G39" s="91" t="inlineStr">
         <is>
           <t>102 °C</t>
         </is>
       </c>
-      <c r="H35" s="93" t="n"/>
-      <c r="I35" s="75" t="n"/>
-    </row>
-    <row r="36" ht="12.75" customHeight="1" s="46"/>
-    <row r="37" ht="12.75" customHeight="1" s="46">
-      <c r="A37" s="94" t="inlineStr">
+      <c r="H39" s="93" t="n"/>
+      <c r="I39" s="75" t="n"/>
+    </row>
+    <row r="40" ht="12.75" customHeight="1" s="46"/>
+    <row r="41" ht="12.75" customHeight="1" s="46">
+      <c r="A41" s="94" t="inlineStr">
         <is>
           <t>PRODOTTO FINITO</t>
         </is>
       </c>
-      <c r="B37" s="95" t="n"/>
-      <c r="C37" s="95" t="n"/>
-    </row>
-    <row r="38" ht="12.75" customHeight="1" s="46">
-      <c r="A38" s="62" t="inlineStr">
+      <c r="B41" s="95" t="n"/>
+      <c r="C41" s="95" t="n"/>
+    </row>
+    <row r="42" ht="12.75" customHeight="1" s="46">
+      <c r="A42" s="62" t="inlineStr">
         <is>
           <t>FORMATO GR</t>
         </is>
       </c>
-      <c r="B38" s="59" t="n"/>
-      <c r="C38" s="96" t="inlineStr">
+      <c r="B42" s="59" t="n"/>
+      <c r="C42" s="96" t="inlineStr">
         <is>
           <t>QUANTITA'
 KG NETTO</t>
         </is>
       </c>
-      <c r="D38" s="97" t="inlineStr">
+      <c r="D42" s="97" t="inlineStr">
         <is>
           <t>PEZZI
 PRODOTTI</t>
         </is>
       </c>
-      <c r="E38" s="97" t="inlineStr">
+      <c r="E42" s="97" t="inlineStr">
         <is>
           <t>LOTTO PRODOTTO 
 FINITO</t>
         </is>
       </c>
-      <c r="F38" s="59" t="n"/>
-      <c r="G38" s="62" t="inlineStr">
+      <c r="F42" s="59" t="n"/>
+      <c r="G42" s="62" t="inlineStr">
         <is>
           <t>SCADENZA</t>
         </is>
       </c>
-      <c r="H38" s="98" t="n"/>
-      <c r="I38" s="59" t="n"/>
-    </row>
-    <row r="39" ht="12.75" customHeight="1" s="46">
-      <c r="A39" s="64" t="n"/>
-      <c r="B39" s="65" t="n"/>
-      <c r="C39" s="64" t="n"/>
-      <c r="D39" s="67" t="n"/>
-      <c r="E39" s="64" t="n"/>
-      <c r="F39" s="65" t="n"/>
-      <c r="G39" s="64" t="n"/>
-      <c r="H39" s="95" t="n"/>
-      <c r="I39" s="65" t="n"/>
-    </row>
-    <row r="40" ht="12.75" customHeight="1" s="46">
-      <c r="A40" s="99" t="n">
+      <c r="H42" s="98" t="n"/>
+      <c r="I42" s="59" t="n"/>
+    </row>
+    <row r="43" ht="12.75" customHeight="1" s="46">
+      <c r="A43" s="64" t="n"/>
+      <c r="B43" s="65" t="n"/>
+      <c r="C43" s="64" t="n"/>
+      <c r="D43" s="67" t="n"/>
+      <c r="E43" s="64" t="n"/>
+      <c r="F43" s="65" t="n"/>
+      <c r="G43" s="64" t="n"/>
+      <c r="H43" s="95" t="n"/>
+      <c r="I43" s="65" t="n"/>
+    </row>
+    <row r="44" ht="12.75" customHeight="1" s="46">
+      <c r="A44" s="99" t="n">
         <v>40</v>
       </c>
-      <c r="B40" s="75" t="n"/>
-      <c r="C40" s="100">
+      <c r="B44" s="75" t="n"/>
+      <c r="C44" s="100">
         <f>D40*A40/1000</f>
-        <v/>
-      </c>
-      <c r="D40" s="99" t="n"/>
-      <c r="E40" s="99" t="n"/>
-      <c r="F40" s="75" t="n"/>
-      <c r="G40" s="101" t="n"/>
-      <c r="H40" s="93" t="n"/>
-      <c r="I40" s="75" t="n"/>
-    </row>
-    <row r="41" ht="12.75" customHeight="1" s="46">
-      <c r="A41" s="99" t="n">
-        <v>212</v>
-      </c>
-      <c r="B41" s="75" t="n"/>
-      <c r="C41" s="100">
-        <f>D41*A41/1000</f>
-        <v/>
-      </c>
-      <c r="D41" s="99" t="n"/>
-      <c r="E41" s="99" t="n"/>
-      <c r="F41" s="75" t="n"/>
-      <c r="G41" s="101" t="n"/>
-      <c r="H41" s="93" t="n"/>
-      <c r="I41" s="75" t="n"/>
-    </row>
-    <row r="42" ht="12.75" customHeight="1" s="46">
-      <c r="A42" s="99" t="n">
-        <v>106</v>
-      </c>
-      <c r="B42" s="75" t="n"/>
-      <c r="C42" s="100">
-        <f>D42*A42/1000</f>
-        <v/>
-      </c>
-      <c r="D42" s="99" t="n"/>
-      <c r="E42" s="99" t="n"/>
-      <c r="F42" s="75" t="n"/>
-      <c r="G42" s="101" t="n"/>
-      <c r="H42" s="93" t="n"/>
-      <c r="I42" s="75" t="n"/>
-    </row>
-    <row r="43" ht="12.75" customHeight="1" s="46">
-      <c r="A43" s="99" t="n"/>
-      <c r="B43" s="75" t="n"/>
-      <c r="C43" s="102">
-        <f>D43*A43/1000</f>
-        <v/>
-      </c>
-      <c r="D43" s="99" t="n"/>
-      <c r="E43" s="99" t="n"/>
-      <c r="F43" s="75" t="n"/>
-      <c r="G43" s="101" t="n"/>
-      <c r="H43" s="93" t="n"/>
-      <c r="I43" s="75" t="n"/>
-    </row>
-    <row r="44" ht="12.75" customHeight="1" s="46">
-      <c r="A44" s="99" t="n"/>
-      <c r="B44" s="75" t="n"/>
-      <c r="C44" s="102">
-        <f>D44*A44/1000</f>
         <v/>
       </c>
       <c r="D44" s="99" t="n"/>
@@ -1868,200 +1870,264 @@
       <c r="I44" s="75" t="n"/>
     </row>
     <row r="45" ht="12.75" customHeight="1" s="46">
-      <c r="A45" s="103" t="n"/>
-      <c r="B45" s="103" t="n"/>
-      <c r="C45" s="104" t="n"/>
+      <c r="A45" s="99" t="n">
+        <v>212</v>
+      </c>
+      <c r="B45" s="75" t="n"/>
+      <c r="C45" s="100">
+        <f>D41*A41/1000</f>
+        <v/>
+      </c>
       <c r="D45" s="99" t="n"/>
       <c r="E45" s="99" t="n"/>
       <c r="F45" s="75" t="n"/>
-      <c r="G45" s="99" t="n"/>
+      <c r="G45" s="101" t="n"/>
       <c r="H45" s="93" t="n"/>
       <c r="I45" s="75" t="n"/>
     </row>
     <row r="46" ht="12.75" customHeight="1" s="46">
-      <c r="A46" s="99" t="n"/>
+      <c r="A46" s="99" t="n">
+        <v>106</v>
+      </c>
       <c r="B46" s="75" t="n"/>
-      <c r="C46" s="104" t="n"/>
+      <c r="C46" s="100">
+        <f>D42*A42/1000</f>
+        <v/>
+      </c>
       <c r="D46" s="99" t="n"/>
       <c r="E46" s="99" t="n"/>
       <c r="F46" s="75" t="n"/>
-      <c r="G46" s="99" t="n"/>
+      <c r="G46" s="101" t="n"/>
       <c r="H46" s="93" t="n"/>
       <c r="I46" s="75" t="n"/>
     </row>
     <row r="47" ht="12.75" customHeight="1" s="46">
       <c r="A47" s="99" t="n"/>
       <c r="B47" s="75" t="n"/>
-      <c r="C47" s="104" t="n"/>
+      <c r="C47" s="102">
+        <f>D43*A43/1000</f>
+        <v/>
+      </c>
       <c r="D47" s="99" t="n"/>
       <c r="E47" s="99" t="n"/>
       <c r="F47" s="75" t="n"/>
-      <c r="G47" s="99" t="n"/>
+      <c r="G47" s="101" t="n"/>
       <c r="H47" s="93" t="n"/>
       <c r="I47" s="75" t="n"/>
     </row>
     <row r="48" ht="12.75" customHeight="1" s="46">
       <c r="A48" s="99" t="n"/>
       <c r="B48" s="75" t="n"/>
-      <c r="C48" s="104" t="n"/>
+      <c r="C48" s="102">
+        <f>D44*A44/1000</f>
+        <v/>
+      </c>
       <c r="D48" s="99" t="n"/>
       <c r="E48" s="99" t="n"/>
       <c r="F48" s="75" t="n"/>
-      <c r="G48" s="99" t="n"/>
+      <c r="G48" s="101" t="n"/>
       <c r="H48" s="93" t="n"/>
       <c r="I48" s="75" t="n"/>
     </row>
-    <row r="49" ht="9.75" customHeight="1" s="46"/>
+    <row r="49" ht="12.75" customHeight="1" s="46">
+      <c r="A49" s="103" t="n"/>
+      <c r="B49" s="103" t="n"/>
+      <c r="C49" s="104" t="n"/>
+      <c r="D49" s="99" t="n"/>
+      <c r="E49" s="99" t="n"/>
+      <c r="F49" s="75" t="n"/>
+      <c r="G49" s="99" t="n"/>
+      <c r="H49" s="93" t="n"/>
+      <c r="I49" s="75" t="n"/>
+    </row>
     <row r="50" ht="12.75" customHeight="1" s="46">
-      <c r="B50" s="105" t="inlineStr">
+      <c r="A50" s="99" t="n"/>
+      <c r="B50" s="75" t="n"/>
+      <c r="C50" s="104" t="n"/>
+      <c r="D50" s="99" t="n"/>
+      <c r="E50" s="99" t="n"/>
+      <c r="F50" s="75" t="n"/>
+      <c r="G50" s="99" t="n"/>
+      <c r="H50" s="93" t="n"/>
+      <c r="I50" s="75" t="n"/>
+    </row>
+    <row r="51" ht="12.75" customHeight="1" s="46">
+      <c r="A51" s="99" t="n"/>
+      <c r="B51" s="75" t="n"/>
+      <c r="C51" s="104" t="n"/>
+      <c r="D51" s="99" t="n"/>
+      <c r="E51" s="99" t="n"/>
+      <c r="F51" s="75" t="n"/>
+      <c r="G51" s="99" t="n"/>
+      <c r="H51" s="93" t="n"/>
+      <c r="I51" s="75" t="n"/>
+    </row>
+    <row r="52" ht="12.75" customHeight="1" s="46">
+      <c r="A52" s="99" t="n"/>
+      <c r="B52" s="75" t="n"/>
+      <c r="C52" s="104" t="n"/>
+      <c r="D52" s="99" t="n"/>
+      <c r="E52" s="99" t="n"/>
+      <c r="F52" s="75" t="n"/>
+      <c r="G52" s="99" t="n"/>
+      <c r="H52" s="93" t="n"/>
+      <c r="I52" s="75" t="n"/>
+    </row>
+    <row r="53" ht="12.75" customHeight="1" s="46"/>
+    <row r="54" ht="12.75" customHeight="1" s="46">
+      <c r="B54" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve"> DATA E FIRMA
 RESPONSABILE DI PRODUZIONE</t>
         </is>
       </c>
-      <c r="C50" s="98" t="n"/>
-      <c r="D50" s="98" t="n"/>
-      <c r="E50" s="59" t="n"/>
-    </row>
-    <row r="51" ht="12.75" customHeight="1" s="46">
-      <c r="B51" s="106" t="n"/>
-      <c r="E51" s="107" t="n"/>
-    </row>
-    <row r="52" ht="9" customHeight="1" s="46">
-      <c r="B52" s="64" t="n"/>
-      <c r="C52" s="95" t="n"/>
-      <c r="D52" s="95" t="n"/>
-      <c r="E52" s="65" t="n"/>
-    </row>
-    <row r="53" ht="12.75" customHeight="1" s="46">
-      <c r="B53" s="87" t="n"/>
-      <c r="C53" s="98" t="n"/>
-      <c r="D53" s="98" t="n"/>
-      <c r="E53" s="59" t="n"/>
-    </row>
-    <row r="54" ht="12.75" customHeight="1" s="46">
-      <c r="B54" s="106" t="n"/>
-      <c r="E54" s="107" t="n"/>
+      <c r="C54" s="98" t="n"/>
+      <c r="D54" s="98" t="n"/>
+      <c r="E54" s="59" t="n"/>
     </row>
     <row r="55" ht="9" customHeight="1" s="46">
-      <c r="B55" s="64" t="n"/>
-      <c r="C55" s="95" t="n"/>
-      <c r="D55" s="95" t="n"/>
-      <c r="E55" s="65" t="n"/>
+      <c r="B55" s="106" t="n"/>
+      <c r="E55" s="107" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="64" t="n"/>
+      <c r="C56" s="95" t="n"/>
+      <c r="D56" s="95" t="n"/>
+      <c r="E56" s="65" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="87" t="n"/>
+      <c r="C57" s="98" t="n"/>
+      <c r="D57" s="98" t="n"/>
+      <c r="E57" s="59" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="106" t="n"/>
+      <c r="E58" s="107" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="64" t="n"/>
+      <c r="C59" s="95" t="n"/>
+      <c r="D59" s="95" t="n"/>
+      <c r="E59" s="65" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="113">
+  <mergeCells count="117">
     <mergeCell ref="D20:E20"/>
-    <mergeCell ref="E8:E9"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="A37:C37"/>
     <mergeCell ref="F16:G16"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D36:E36"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="G8:I9"/>
-    <mergeCell ref="A38:B39"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="E49:F49"/>
     <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="G52:I52"/>
     <mergeCell ref="B24:C24"/>
+    <mergeCell ref="E42:F43"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="G42:I42"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E12:E13"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A1:I3"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="D35:E35"/>
     <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A12:B13"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D34:E34"/>
     <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G12:I13"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="E48:F48"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="A46:B46"/>
-    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="G51:I51"/>
     <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B50:E52"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F28:G28"/>
-    <mergeCell ref="G43:I43"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="D23:E23"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="E39:F39"/>
     <mergeCell ref="E44:F44"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A42:B43"/>
+    <mergeCell ref="B54:E56"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="G45:I45"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G42:I43"/>
+    <mergeCell ref="A4:I4"/>
     <mergeCell ref="G47:I47"/>
-    <mergeCell ref="G38:I39"/>
     <mergeCell ref="G44:I44"/>
     <mergeCell ref="E46:F46"/>
     <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="G46:I46"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="G40:I40"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D42:D43"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="A43:B43"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="E38:F39"/>
-    <mergeCell ref="C5:I6"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="B53:E55"/>
-    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="A9:I10"/>
     <mergeCell ref="D21:E21"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="F12:G12"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="G35:I35"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="A50:B50"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A5:I7"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="E45:F45"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="B57:E59"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="G48:I48"/>
     <mergeCell ref="E47:F47"/>
